--- a/y11581/samples/refund_records.xlsx
+++ b/y11581/samples/refund_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>member_id</t>
   </si>
@@ -43,6 +43,12 @@
     <t>reviewer</t>
   </si>
   <si>
+    <t>is_cross_store</t>
+  </si>
+  <si>
+    <t>is_revoked</t>
+  </si>
+  <si>
     <t>M001</t>
   </si>
   <si>
@@ -61,6 +67,9 @@
     <t>M999</t>
   </si>
   <si>
+    <t>M010</t>
+  </si>
+  <si>
     <t>会员1号</t>
   </si>
   <si>
@@ -79,6 +88,9 @@
     <t>超额退款</t>
   </si>
   <si>
+    <t>跨店退款</t>
+  </si>
+  <si>
     <t>S02</t>
   </si>
   <si>
@@ -97,12 +109,12 @@
     <t>门店1</t>
   </si>
   <si>
+    <t>会员退卡</t>
+  </si>
+  <si>
     <t>活动取消</t>
   </si>
   <si>
-    <t>会员退卡</t>
-  </si>
-  <si>
     <t>储值退款</t>
   </si>
   <si>
@@ -112,19 +124,19 @@
     <t>缺字段退款</t>
   </si>
   <si>
-    <t>2024-01-07 14:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-26 16:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-15 19:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-07 11:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-12 18:00:00</t>
+    <t>2024-01-25 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-09 15:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-30 19:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-29 18:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-29 19:00:00</t>
   </si>
   <si>
     <t>2024-01-20 16:00:00</t>
@@ -133,19 +145,22 @@
     <t>2024-01-21 11:30:00</t>
   </si>
   <si>
+    <t>2024-01-28 14:00:00</t>
+  </si>
+  <si>
+    <t>营业员B</t>
+  </si>
+  <si>
     <t>营业员A</t>
   </si>
   <si>
     <t>营业员C</t>
   </si>
   <si>
-    <t>营业员B</t>
+    <t>主管Y</t>
   </si>
   <si>
     <t>主管X</t>
-  </si>
-  <si>
-    <t>主管Y</t>
   </si>
 </sst>
 </file>
@@ -503,10 +518,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,199 +549,282 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2">
+        <v>85</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>198</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>138</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2">
-        <v>164</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3">
-        <v>164</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>56</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>78</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <v>149</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>99999</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="C8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>150</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
